--- a/AAII_Financials/Yearly/BEKAY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BEKAY_YR_FIN.xlsx
@@ -652,6 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A5:K102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
